--- a/stories/arbres/TREE-SAN-009.xlsx
+++ b/stories/arbres/TREE-SAN-009.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Tom est dans le salon. Un dessin danse à l'écran. Maman s'assoit près de lui. Papa est là aussi. L'adulte dit fini. Tom va éteindre. Puis il prend un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tom a croqué une pomme. Puis le dessin. Maman dit : fini. L'adulte dit fini. Tom éteint l'écran. L'écran devient noir. Maman dit : un autre jeu. Tom cherche.</t>
+          <t>Tom a croqué une pomme. Puis le dessin. Fini. L'adulte dit fini. Tom éteint l'écran. L'écran devient noir. Un autre jeu. Tom cherche.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,15 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a croqué une pomme. Puis le dessin.
+maman|Fini. L'adulte dit fini.
+narrateur|Tom éteint l'écran. L'écran devient noir.
+maman|Un autre jeu.
+narrateur|Tom cherche.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1861,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman dit fini. Que fait Tom ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2034,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a éteint. L'adulte a dit fini. Un autre jeu commence.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2225,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2392,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va à la cuisine. L'écran est éteint. L'adulte a dit fini. Il prend un autre jeu. Des cuillères en bois. Papa joue aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2583,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2750,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Tom empile les cubes. Il a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2917,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3084,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Tom ouvre le livre. Il a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3251,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3418,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Tom fait la dînette. Il a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3585,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3752,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va au jardin. L'écran est éteint. L'adulte a dit fini. Un autre jeu dehors. Le ballon. Maman lance.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3943,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4110,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Tom pose des cubes sur la table du jardin. Il a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4277,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4444,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Tom lit un livre sur l'herbe. Il a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4611,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4778,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Tom sort la dînette. Il a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4945,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5112,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va dans la chambre. L'écran est éteint. L'adulte a dit fini. Un autre jeu sur le tapis. Papa s'assoit.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5303,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5470,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Tom bâtit une tour de cubes. Il a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5637,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5804,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Tom écoute le livre. Il a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5971,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6138,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Tom sert le doudou à la dînette. Il a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6305,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6163,7 +6334,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Tom a mangé un yaourt. Puis l'écran. Papa dit : fini. L'adulte dit fini. Tom éteint. Il pose la télécommande. Papa dit : un autre jeu.</t>
+          <t>Tom a mangé un yaourt. Puis l'écran. Fini. L'adulte dit fini. Tom éteint. Il pose la télécommande. Un autre jeu.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6301,6 +6472,14 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a mangé un yaourt. Puis l'écran.
+papa|Fini. L'adulte dit fini.
+narrateur|Tom éteint. Il pose la télécommande.
+papa|Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6656,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Papa dit fini. Que fait Tom ?</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6829,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a éteint. L'adulte a dit fini. Le yaourt est fini aussi. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7020,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7187,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|À la cuisine, Tom range le pot. L'écran est éteint. L'adulte a dit fini. Un autre jeu : trier les cuillères.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7378,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7545,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Cubes sur la table. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7712,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7879,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Un livre de recettes imagées. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8046,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8213,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|La dînette près du buffet. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8380,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8547,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Au jardin, Tom court un peu. Il a éteint. L'adulte a dit fini. Un autre jeu, dehors.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8738,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8905,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Cubes au soleil. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9072,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9239,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Un livre sous le cerisier. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9406,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9573,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Dînette sur la nappe. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9740,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9907,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la chambre, Tom s'étire. L'écran est éteint. L'adulte a dit fini. Un autre jeu sur le tapis.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10098,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10265,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Une tour de cubes. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10432,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10599,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Le livre des animaux. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10766,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10933,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|La dînette des peluches. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11100,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10815,7 +11129,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Tom a mangé un morceau de pain. Puis l'écran. Maman dit : fini. L'adulte dit fini. Tom éteint. Il sourit un peu. Maman dit : un autre jeu, maintenant.</t>
+          <t>Tom a mangé un morceau de pain. Puis l'écran. Fini. L'adulte dit fini. Tom éteint. Il sourit un peu. Un autre jeu, maintenant.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10953,6 +11267,14 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a mangé un morceau de pain. Puis l'écran.
+maman|Fini. L'adulte dit fini.
+narrateur|Tom éteint. Il sourit un peu.
+maman|Un autre jeu, maintenant.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11133,6 +11455,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|L'adulte dit fini. Que fait Tom ?</t>
         </is>
       </c>
     </row>
@@ -11301,6 +11628,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Le pain est fini. L'écran aussi. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11487,6 +11819,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11649,6 +11986,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|À la cuisine, Tom essuie des miettes. L'écran est éteint. L'adulte a dit fini. Un autre jeu avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11835,6 +12177,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11997,6 +12344,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Cubes et miettes rangées. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12159,6 +12511,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12321,6 +12678,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Un livre sur la table. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12483,6 +12845,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12645,6 +13012,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Dînette après le pain. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12807,6 +13179,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12969,6 +13346,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Au jardin, Tom cherche un caillou rond. Il a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13155,6 +13537,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13317,6 +13704,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Cubes près des cailloux. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13479,6 +13871,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13641,6 +14038,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Un livre sur le banc. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13803,6 +14205,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13965,6 +14372,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Dînette sous le tilleul. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14127,6 +14539,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14289,6 +14706,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la chambre, Tom range une chaussette. L'écran est éteint. L'adulte a dit fini. Un autre jeu, tout calme.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14475,6 +14897,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14637,6 +15064,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Cubes au pied du lit. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14799,6 +15231,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14961,6 +15398,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Le livre sous la lampe. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15123,6 +15565,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15285,6 +15732,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|La dînette des doudous. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15447,6 +15899,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15465,7 +15922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15482,6 +15939,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SAN-009.xlsx
+++ b/stories/arbres/TREE-SAN-009.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Tom est dans le salon. Un dessin danse à l'écran. Maman s'assoit près de lui. Papa est là aussi. L'adulte dit fini. Tom va éteindre. Puis il prend un autre jeu.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
 narrateur|Tom cherche.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1868,6 +1876,7 @@
           <t>narrateur|Maman dit fini. Que fait Tom ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2039,6 +2048,7 @@
           <t>narrateur|Tom a éteint. L'adulte a dit fini. Un autre jeu commence.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2230,6 +2240,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2397,6 +2408,7 @@
           <t>narrateur|Tom va à la cuisine. L'écran est éteint. L'adulte a dit fini. Il prend un autre jeu. Des cuillères en bois. Papa joue aussi.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2588,6 +2600,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2755,6 +2768,7 @@
           <t>narrateur|Tom empile les cubes. Il a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2922,6 +2936,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3089,6 +3104,7 @@
           <t>narrateur|Tom ouvre le livre. Il a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3256,6 +3272,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3423,6 +3440,7 @@
           <t>narrateur|Tom fait la dînette. Il a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3590,6 +3608,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3757,6 +3776,7 @@
           <t>narrateur|Tom va au jardin. L'écran est éteint. L'adulte a dit fini. Un autre jeu dehors. Le ballon. Maman lance.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3948,6 +3968,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4115,6 +4136,7 @@
           <t>narrateur|Tom pose des cubes sur la table du jardin. Il a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4282,6 +4304,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4449,6 +4472,7 @@
           <t>narrateur|Tom lit un livre sur l'herbe. Il a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4616,6 +4640,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4783,6 +4808,7 @@
           <t>narrateur|Tom sort la dînette. Il a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4950,6 +4976,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5117,6 +5144,7 @@
           <t>narrateur|Tom va dans la chambre. L'écran est éteint. L'adulte a dit fini. Un autre jeu sur le tapis. Papa s'assoit.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5308,6 +5336,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5475,6 +5504,7 @@
           <t>narrateur|Tom bâtit une tour de cubes. Il a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5642,6 +5672,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5809,6 +5840,7 @@
           <t>narrateur|Tom écoute le livre. Il a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5976,6 +6008,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6143,6 +6176,7 @@
           <t>narrateur|Tom sert le doudou à la dînette. Il a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6310,6 +6344,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6480,6 +6515,7 @@
 papa|Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6663,6 +6699,7 @@
           <t>narrateur|Papa dit fini. Que fait Tom ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6834,6 +6871,7 @@
           <t>narrateur|Tom a éteint. L'adulte a dit fini. Le yaourt est fini aussi. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7025,6 +7063,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7192,6 +7231,7 @@
           <t>narrateur|À la cuisine, Tom range le pot. L'écran est éteint. L'adulte a dit fini. Un autre jeu : trier les cuillères.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7383,6 +7423,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7550,6 +7591,7 @@
           <t>narrateur|Cubes sur la table. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7717,6 +7759,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7884,6 +7927,7 @@
           <t>narrateur|Un livre de recettes imagées. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8051,6 +8095,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8218,6 +8263,7 @@
           <t>narrateur|La dînette près du buffet. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8385,6 +8431,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8552,6 +8599,7 @@
           <t>narrateur|Au jardin, Tom court un peu. Il a éteint. L'adulte a dit fini. Un autre jeu, dehors.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8743,6 +8791,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8910,6 +8959,7 @@
           <t>narrateur|Cubes au soleil. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9077,6 +9127,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9244,6 +9295,7 @@
           <t>narrateur|Un livre sous le cerisier. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9411,6 +9463,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9578,6 +9631,7 @@
           <t>narrateur|Dînette sur la nappe. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9745,6 +9799,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9912,6 +9967,7 @@
           <t>narrateur|Dans la chambre, Tom s'étire. L'écran est éteint. L'adulte a dit fini. Un autre jeu sur le tapis.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10103,6 +10159,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10270,6 +10327,7 @@
           <t>narrateur|Une tour de cubes. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10437,6 +10495,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10604,6 +10663,7 @@
           <t>narrateur|Le livre des animaux. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10771,6 +10831,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10938,6 +10999,7 @@
           <t>narrateur|La dînette des peluches. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11105,6 +11167,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11275,6 +11338,7 @@
 maman|Un autre jeu, maintenant.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11462,6 +11526,7 @@
           <t>narrateur|L'adulte dit fini. Que fait Tom ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11633,6 +11698,7 @@
           <t>narrateur|Le pain est fini. L'écran aussi. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11824,6 +11890,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11991,6 +12058,7 @@
           <t>narrateur|À la cuisine, Tom essuie des miettes. L'écran est éteint. L'adulte a dit fini. Un autre jeu avec papa.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12182,6 +12250,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12349,6 +12418,7 @@
           <t>narrateur|Cubes et miettes rangées. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12516,6 +12586,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12683,6 +12754,7 @@
           <t>narrateur|Un livre sur la table. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12850,6 +12922,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13017,6 +13090,7 @@
           <t>narrateur|Dînette après le pain. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13184,6 +13258,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13351,6 +13426,7 @@
           <t>narrateur|Au jardin, Tom cherche un caillou rond. Il a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13542,6 +13618,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13709,6 +13786,7 @@
           <t>narrateur|Cubes près des cailloux. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13876,6 +13954,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14043,6 +14122,7 @@
           <t>narrateur|Un livre sur le banc. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14210,6 +14290,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14377,6 +14458,7 @@
           <t>narrateur|Dînette sous le tilleul. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14544,6 +14626,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14711,6 +14794,7 @@
           <t>narrateur|Dans la chambre, Tom range une chaussette. L'écran est éteint. L'adulte a dit fini. Un autre jeu, tout calme.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14902,6 +14986,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15069,6 +15154,7 @@
           <t>narrateur|Cubes au pied du lit. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15236,6 +15322,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15403,6 +15490,7 @@
           <t>narrateur|Le livre sous la lampe. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15570,6 +15658,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15737,6 +15826,7 @@
           <t>narrateur|La dînette des doudous. Tom a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15904,6 +15994,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15922,7 +16013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15946,6 +16037,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15960,7 +16065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16147,6 +16252,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
